--- a/artfynd/A 56996-2025 artfynd.xlsx
+++ b/artfynd/A 56996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106158589</v>
+        <v>127473475</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801760.5662128414</v>
+        <v>801762</v>
       </c>
       <c r="R2" t="n">
-        <v>7178785.429974351</v>
+        <v>7178781</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,27 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,6 +761,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,44 +773,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106158579</v>
+        <v>106159396</v>
       </c>
       <c r="B3" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -847,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801760.7363885303</v>
+        <v>801774</v>
       </c>
       <c r="R3" t="n">
-        <v>7178779.398336975</v>
+        <v>7178705</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,15 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106158523</v>
+        <v>127473847</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801745.0114326914</v>
+        <v>801773</v>
       </c>
       <c r="R4" t="n">
-        <v>7178746.287417027</v>
+        <v>7178704</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,22 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,7 +983,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1043,12 +993,7 @@
         <v>106158556</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>801752.8098363741</v>
+        <v>801753</v>
       </c>
       <c r="R5" t="n">
-        <v>7178763.484571454</v>
+        <v>7178763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,19 +1065,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106159396</v>
+        <v>127443985</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,44 +1106,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norra Långgrundet, Vb</t>
+          <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801774.6849454721</v>
+        <v>801754</v>
       </c>
       <c r="R6" t="n">
-        <v>7178704.7511448</v>
+        <v>7178761</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,22 +1160,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,56 +1174,54 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106158546</v>
+        <v>127473284</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1327,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>801752.8098363741</v>
+        <v>801740</v>
       </c>
       <c r="R7" t="n">
-        <v>7178763.484571454</v>
+        <v>7178839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,22 +1268,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,55 +1294,59 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Patrik Nygren, Tommy Boström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127443984</v>
+        <v>106158546</v>
       </c>
       <c r="B8" t="n">
-        <v>91920</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långgrunden, Vb</t>
+          <t>Norra Långgrundet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>801754</v>
+        <v>801753</v>
       </c>
       <c r="R8" t="n">
-        <v>7178761</v>
+        <v>7178763</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,12 +1373,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,26 +1394,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127443985</v>
+        <v>127473446</v>
       </c>
       <c r="B9" t="n">
-        <v>91549</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,34 +1417,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långgrunden, Vb</t>
+          <t>Norra Långgrundet, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801754</v>
+        <v>801768</v>
       </c>
       <c r="R9" t="n">
-        <v>7178761</v>
+        <v>7178786</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,75 +1492,67 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren, Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127473312</v>
+        <v>127443984</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>92281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norra Långgrundet, Vb</t>
+          <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>801744</v>
+        <v>801754</v>
       </c>
       <c r="R10" t="n">
-        <v>7178833</v>
+        <v>7178761</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1687,71 +1587,70 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127473265</v>
+        <v>106158579</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1759,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>801702</v>
+        <v>801761</v>
       </c>
       <c r="R11" t="n">
-        <v>7178759</v>
+        <v>7178780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,17 +1688,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>hack i gran</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,6 +1702,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1826,14 +1721,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127473233</v>
+        <v>106158589</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1859,7 +1754,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1869,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801724</v>
+        <v>801760</v>
       </c>
       <c r="R12" t="n">
-        <v>7178735</v>
+        <v>7178785</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,12 +1794,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2019-09-11</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1936,41 +1831,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127473813</v>
+        <v>127473233</v>
       </c>
       <c r="B13" t="n">
-        <v>91370</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1978,10 +1874,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801740</v>
+        <v>801724</v>
       </c>
       <c r="R13" t="n">
-        <v>7178750</v>
+        <v>7178735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,13 +1912,17 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2034,48 +1934,49 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127473847</v>
+        <v>127473265</v>
       </c>
       <c r="B14" t="n">
-        <v>91348</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2083,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801773</v>
+        <v>801702</v>
       </c>
       <c r="R14" t="n">
-        <v>7178704</v>
+        <v>7178759</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,13 +2022,17 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2139,48 +2044,49 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127473475</v>
+        <v>127473312</v>
       </c>
       <c r="B15" t="n">
-        <v>91648</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2188,10 +2094,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>801762</v>
+        <v>801744</v>
       </c>
       <c r="R15" t="n">
-        <v>7178781</v>
+        <v>7178833</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2226,13 +2132,17 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>hack i gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2244,220 +2154,10 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>127473284</v>
-      </c>
-      <c r="B16" t="n">
-        <v>91352</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Norra Långgrundet, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>801740</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7178839</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren, Tommy Boström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127473446</v>
-      </c>
-      <c r="B17" t="n">
-        <v>91806</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phlebia centrifuga</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Norra Långgrundet, Vb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>801768</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7178786</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56996-2025 artfynd.xlsx
+++ b/artfynd/A 56996-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473475</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106159396</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106158556</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127443985</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1298,6 +1328,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473284</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106158546</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127443984</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106158579</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1828,6 +1883,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106158589</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473233</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473265</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2158,8 +2228,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127473312</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>